--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:06</t>
+          <t>2026-09-03 00:54:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:07</t>
+          <t>2026-09-03 00:54:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:09</t>
+          <t>2026-09-03 00:54:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:35:10</t>
+          <t>2026-09-03 00:54:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:19</t>
+          <t>2026-09-03 01:13:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:20</t>
+          <t>2026-09-03 01:13:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:22</t>
+          <t>2026-09-03 01:13:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:23</t>
+          <t>2026-09-03 01:14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:23</t>
+          <t>2026-09-03 01:14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:23</t>
+          <t>2026-09-03 01:14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:23</t>
+          <t>2026-09-03 01:14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:54:23</t>
+          <t>2026-09-03 01:14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.64%364,000</t>
+          <t>7.75%364,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>7.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.31%480,000</t>
+          <t>7.65%480,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>7.65%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.58%558,000</t>
+          <t>6.76%558,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>6.76%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.37%310,000</t>
+          <t>6.39%310,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.37%</t>
+          <t>6.39%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.44%1,570,000</t>
+          <t>5.32%1,570,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5290</v>
+        <v>2100</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.14%273,000</t>
+          <t>5.13%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>273000</v>
+        <v>665000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2170</v>
+        <v>5045</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.14%665,000</t>
+          <t>5.06%273,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>665000</v>
+        <v>273000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>-6.38%1100</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-6.38%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1175</v>
+        <v>1100</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.72%1,127,000</t>
+          <t>4.55%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.11%212,000</t>
+          <t>4.12%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.03%529,000</t>
+          <t>4.06%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17725</v>
+        <v>17850</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.43%54,300</t>
+          <t>3.56%54,300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-2.47%3350</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1200</v>
+        <v>3350</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.16%739,000</t>
+          <t>3.01%245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>739000</v>
+        <v>245000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.92%3435</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3435</v>
+        <v>1080</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.00%245,000</t>
+          <t>2.93%739,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>245000</v>
+        <v>739000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.1%957</t>
+          <t>+2.8%5870</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>957</v>
+        <v>5870</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.56%750,000</t>
+          <t>2.59%120,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>750000</v>
+        <v>120000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:56</t>
+          <t>2026-09-03 21:26:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.73%5710</t>
+          <t>-4.7%912</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5710</v>
+        <v>912</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%120,000</t>
+          <t>2.51%750,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>120000</v>
+        <v>750000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.57%530</t>
+          <t>-8.58%484.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-8.58%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>530</v>
+        <v>484.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.26%1,200,000</t>
+          <t>2.13%1,200,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-0.71%2095</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>13865</v>
+        <v>2095</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.07%42,000</t>
+          <t>2.08%271,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>42000</v>
+        <v>271000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2110</v>
+        <v>13450</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.04%271,000</t>
+          <t>2.07%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>271000</v>
+        <v>42000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3395</v>
+        <v>3120</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.91%158,400</t>
+          <t>1.81%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1410</v>
+        <v>2390</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.54%306,000</t>
+          <t>1.57%179,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>306000</v>
+        <v>179000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2385</v>
+        <v>1345</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%179,000</t>
+          <t>1.51%306,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.95%2795</t>
+          <t>-3.04%2710</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2795</v>
+        <v>2710</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.68%602</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>602</v>
+        <v>2475</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.39%650,000</t>
+          <t>1.35%149,139</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>650000</v>
+        <v>149139</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-7.97%554</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-7.97%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2610</v>
+        <v>554</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.39%149,139</t>
+          <t>1.32%650,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>149139</v>
+        <v>650000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.02%2405</t>
+          <t>-1.66%2365</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2405</v>
+        <v>2365</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.30%152,000</t>
+          <t>1.32%152,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.27%282,000</t>
+          <t>1.23%282,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.25%199.5</t>
+          <t>-4.01%191.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>199.5</v>
+        <v>191.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.99%1,400,000</t>
+          <t>0.98%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-2.99%1300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1340</v>
+        <v>1300</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.58%94,000</t>
+          <t>0.61%94,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:57</t>
+          <t>2026-09-03 21:27:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.22%968</t>
+          <t>-0.71%7000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>968</v>
+        <v>7000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.58%168,000</t>
+          <t>0.59%23,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>168000</v>
+        <v>23000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.03%7050</t>
+          <t>-2.07%948</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7050</v>
+        <v>948</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.58%23,000</t>
+          <t>0.58%168,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>23000</v>
+        <v>168000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%609</t>
+          <t>-3.94%585</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-4.14%927</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.38%110,000</t>
+          <t>0.37%110,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.41%245.5</t>
+          <t>-4.89%233.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-4.89%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>245.5</v>
+        <v>233.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.35%400,000</t>
+          <t>0.34%400,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.15%646</t>
+          <t>-2.48%630</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-2.48%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.5%787</t>
+          <t>-3.56%759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.27%95,000</t>
+          <t>0.26%95,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.61%149.5</t>
+          <t>-1.67%147</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.99%242</t>
+          <t>-4.55%231</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>-3.51%261</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>270.5</v>
+        <v>261</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3163波若威</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.66%766</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>766</v>
+        <v>125</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.04%13,300</t>
+          <t>0.04%78,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>13300</v>
+        <v>78000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3163波若威</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-6.01%720</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-6.01%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>126</v>
+        <v>720</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.03%78,000</t>
+          <t>0.04%13,300</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>78000</v>
+        <v>13300</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.68%233.5</t>
+          <t>-3.21%226</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>233.5</v>
+        <v>226</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2%459</t>
+          <t>-9.91%413.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2%</t>
+          <t>-9.91%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>459</v>
+        <v>413.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.75%4200</t>
+          <t>0%4050</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:58</t>
+          <t>2026-09-03 21:27:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.67%692</t>
+          <t>-2.6%674</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:00</t>
+          <t>2026-09-03 21:27:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:00</t>
+          <t>2026-09-03 21:27:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.29%1705</t>
+          <t>-2.05%1670</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1705</v>
+        <v>1670</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:00</t>
+          <t>2026-09-03 21:27:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.36%1445</t>
+          <t>-2.77%1405</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:00</t>
+          <t>2026-09-03 21:27:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.46%1395</t>
+          <t>-1.43%1375</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:14:00</t>
+          <t>2026-09-03 21:27:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.73%245.5</t>
+          <t>-3.67%236.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-3.67%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>245.5</v>
+        <v>236.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:26:58</t>
+          <t>2026-09-03 21:41:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:00</t>
+          <t>2026-09-03 21:41:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:01</t>
+          <t>2026-09-03 21:41:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:02</t>
+          <t>2026-09-03 21:41:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:02</t>
+          <t>2026-09-03 21:41:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:02</t>
+          <t>2026-09-03 21:41:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:02</t>
+          <t>2026-09-03 21:41:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:27:02</t>
+          <t>2026-09-03 21:41:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:39</t>
+          <t>2026-09-03 21:58:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:40</t>
+          <t>2026-09-03 21:58:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:41</t>
+          <t>2026-09-03 21:58:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:42</t>
+          <t>2026-09-03 21:58:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:42</t>
+          <t>2026-09-03 21:58:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:42</t>
+          <t>2026-09-03 21:58:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:42</t>
+          <t>2026-09-03 21:58:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:41:42</t>
+          <t>2026-09-03 21:58:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:53</t>
+          <t>2026-09-03 22:32:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:55</t>
+          <t>2026-09-03 22:32:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:56</t>
+          <t>2026-09-03 22:32:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:57</t>
+          <t>2026-09-03 22:32:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:57</t>
+          <t>2026-09-03 22:32:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:57</t>
+          <t>2026-09-03 22:32:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:57</t>
+          <t>2026-09-03 22:32:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:58:57</t>
+          <t>2026-09-03 22:32:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:52</t>
+          <t>2026-09-03 22:45:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:53</t>
+          <t>2026-09-03 22:45:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:55</t>
+          <t>2026-09-03 22:45:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:56</t>
+          <t>2026-09-03 22:45:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:56</t>
+          <t>2026-09-03 22:45:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:56</t>
+          <t>2026-09-03 22:45:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:56</t>
+          <t>2026-09-03 22:45:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:56</t>
+          <t>2026-09-03 22:45:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:19</t>
+          <t>2026-09-03 23:01:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:20</t>
+          <t>2026-09-03 23:01:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:22</t>
+          <t>2026-09-03 23:01:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:45:23</t>
+          <t>2026-09-03 23:01:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
